--- a/MMT_Automation/src/test/resources/data/Villas_TestData.xlsx
+++ b/MMT_Automation/src/test/resources/data/Villas_TestData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{E270284A-1C8D-446F-9857-92230E45C29F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{44523FCA-C28B-4D76-9D9B-A584AE7F71C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
